--- a/swing_strategy_vix_sim_balanced_20260228.xlsx
+++ b/swing_strategy_vix_sim_balanced_20260228.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -578,56 +578,56 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>KMI</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>86.66</v>
+        <v>33.27</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>85.57 - 86.77</t>
+          <t>32.95 - 33.41</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86.17</v>
+        <v>33.18</v>
       </c>
       <c r="F2" t="n">
-        <v>81.45</v>
+        <v>31.46</v>
       </c>
       <c r="G2" t="n">
-        <v>90.79000000000001</v>
+        <v>34.44</v>
       </c>
       <c r="H2" t="n">
-        <v>82.48999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>0.41</v>
+        <v>0.49</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="L2" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="O2" t="n">
-        <v>0.73</v>
+        <v>0.08</v>
       </c>
       <c r="P2" t="n">
-        <v>84023820288</v>
+        <v>72906907648</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -667,56 +667,56 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>PSMT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.25</v>
+        <v>154.62</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16.04 - 16.26</t>
+          <t>152.70 - 154.83</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16.15</v>
+        <v>153.76</v>
       </c>
       <c r="F3" t="n">
-        <v>15.31</v>
+        <v>145.76</v>
       </c>
       <c r="G3" t="n">
-        <v>19.2</v>
+        <v>159.63</v>
       </c>
       <c r="H3" t="n">
-        <v>78.62</v>
+        <v>84.38</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.27</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.25</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="N3" t="n">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.31</v>
       </c>
       <c r="P3" t="n">
-        <v>11657420800</v>
+        <v>4840633856</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>99.01000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -756,56 +756,56 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KMI</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33.06</v>
+        <v>658.08</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32.78 - 33.24</t>
+          <t>649.95 - 659.03</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>33.01</v>
+        <v>654.49</v>
       </c>
       <c r="F4" t="n">
-        <v>31.3</v>
+        <v>620.4299999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>34.26</v>
+        <v>679.46</v>
       </c>
       <c r="H4" t="n">
-        <v>73.94</v>
+        <v>84.16</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>0.49</v>
+        <v>1.55</v>
       </c>
       <c r="K4" t="n">
-        <v>0.49</v>
+        <v>1.61</v>
       </c>
       <c r="L4" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1</v>
+        <v>0.77</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08</v>
+        <v>0.62</v>
       </c>
       <c r="P4" t="n">
-        <v>72906907648</v>
+        <v>148541177856</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>98.34</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>机构偏多</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
@@ -845,56 +845,56 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RCI</t>
+          <t>FOLD</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>39.41</v>
+        <v>14.37</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>39.24 - 39.78</t>
+          <t>14.24 - 14.44</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>39.51</v>
+        <v>14.34</v>
       </c>
       <c r="F5" t="n">
-        <v>37.47</v>
+        <v>13.6</v>
       </c>
       <c r="G5" t="n">
-        <v>41.01</v>
+        <v>14.89</v>
       </c>
       <c r="H5" t="n">
-        <v>71.83</v>
+        <v>87.63</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>0.33</v>
+        <v>-0.88</v>
       </c>
       <c r="K5" t="n">
-        <v>0.37</v>
+        <v>-0.96</v>
       </c>
       <c r="L5" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4</v>
+        <v>-0.12</v>
       </c>
       <c r="N5" t="n">
-        <v>0.65</v>
+        <v>1.04</v>
       </c>
       <c r="O5" t="n">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>21593073664</v>
+        <v>4498514944</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -903,16 +903,16 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>99.98</v>
+        <v>95.45</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>明确吸筹</t>
+          <t>极度缩量(隐蔽吸筹)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>strong_uptrend</t>
+          <t>uptrend</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>机构偏多</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
@@ -934,52 +934,52 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>58.16</v>
+        <v>873.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>57.78 - 58.59</t>
+          <t>858.62 - 870.67</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>58.18</v>
+        <v>864.64</v>
       </c>
       <c r="F6" t="n">
-        <v>55.17</v>
+        <v>808.6799999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>60.39</v>
+        <v>911.8</v>
       </c>
       <c r="H6" t="n">
-        <v>68.41</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.34</v>
+        <v>6.57</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.34</v>
+        <v>6.72</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.19</v>
+        <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0.11</v>
+        <v>0.43</v>
       </c>
       <c r="N6" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="O6" t="n">
-        <v>0.22</v>
+        <v>1.06</v>
       </c>
       <c r="P6" t="n">
-        <v>1830904832</v>
+        <v>237679427584</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -992,11 +992,11 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>84.36</v>
+        <v>86.47</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>极度缩量(隐蔽吸筹)</t>
+          <t>明确吸筹</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>防御性对冲</t>
         </is>
       </c>
     </row>
@@ -1023,56 +1023,56 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JBS</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.63</v>
+        <v>113.46</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16.36 - 16.59</t>
+          <t>111.73 - 113.29</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.48</v>
+        <v>112.51</v>
       </c>
       <c r="F7" t="n">
-        <v>15.62</v>
+        <v>106.64</v>
       </c>
       <c r="G7" t="n">
-        <v>17.11</v>
+        <v>116.82</v>
       </c>
       <c r="H7" t="n">
-        <v>65.93000000000001</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.16</v>
+        <v>-0.38</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.16</v>
+        <v>-0.39</v>
       </c>
       <c r="L7" t="n">
-        <v>0.13</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2</v>
+        <v>0.85</v>
       </c>
       <c r="O7" t="n">
-        <v>0.12</v>
+        <v>0.38</v>
       </c>
       <c r="P7" t="n">
-        <v>18199644160</v>
+        <v>133326643200</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>77.95999999999999</v>
+        <v>85.56</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>机构偏多</t>
         </is>
       </c>
     </row>
@@ -1112,56 +1112,53 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>DBRG</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31.77</v>
+        <v>15.45</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>31.55 - 31.99</t>
+          <t>15.32 - 15.54</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31.77</v>
+        <v>15.43</v>
       </c>
       <c r="F8" t="n">
-        <v>29.88</v>
+        <v>14.63</v>
       </c>
       <c r="G8" t="n">
-        <v>32.98</v>
+        <v>16.02</v>
       </c>
       <c r="H8" t="n">
-        <v>65.84999999999999</v>
+        <v>81.37</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.28</v>
+        <v>1.28</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.09</v>
+        <v>-0.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.04</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8</v>
+        <v>-0.39</v>
       </c>
       <c r="P8" t="n">
-        <v>1316700544</v>
+        <v>2995012352</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1170,16 +1167,16 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>65.81</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>明确吸筹</t>
+          <t>极度缩量(隐蔽吸筹)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>strong_uptrend</t>
+          <t>uptrend</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1189,7 +1186,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>防御性对冲</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
@@ -1201,56 +1198,56 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CP</t>
+          <t>ATO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>87.12</v>
+        <v>186.79</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>86.18 - 87.39</t>
+          <t>184.94 - 187.51</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>86.78</v>
+        <v>186.23</v>
       </c>
       <c r="F9" t="n">
-        <v>82.27</v>
+        <v>176.56</v>
       </c>
       <c r="G9" t="n">
-        <v>91.66</v>
+        <v>193.32</v>
       </c>
       <c r="H9" t="n">
-        <v>65.34999999999999</v>
+        <v>68.34</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1</v>
+        <v>0.14</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="M9" t="n">
         <v>0.09</v>
       </c>
       <c r="N9" t="n">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.39</v>
+        <v>-0.9</v>
       </c>
       <c r="P9" t="n">
-        <v>77368631296</v>
+        <v>30119813120</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1259,7 +1256,7 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>62.23</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1278,7 +1275,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>防御性对冲</t>
+          <t>机构偏多</t>
         </is>
       </c>
     </row>
@@ -1290,65 +1287,65 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>48.24</v>
+        <v>56.42</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.99 - 48.66</t>
+          <t>56.39 - 57.17</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48.32</v>
+        <v>56.78</v>
       </c>
       <c r="F10" t="n">
-        <v>45.82</v>
+        <v>53.86</v>
       </c>
       <c r="G10" t="n">
-        <v>50.81</v>
+        <v>60.46</v>
       </c>
       <c r="H10" t="n">
-        <v>98.98</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0.09</v>
+        <v>-0.34</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.32</v>
+        <v>-0.34</v>
       </c>
       <c r="L10" t="n">
-        <v>0.68</v>
+        <v>-0.19</v>
       </c>
       <c r="M10" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7</v>
+        <v>1.02</v>
       </c>
       <c r="O10" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="P10" t="n">
-        <v>22566311936</v>
+        <v>1830904832</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>仅跟踪</t>
+          <t>主升浪建仓/加仓</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>56.06</v>
+        <v>74.52</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1362,12 +1359,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>extended(超买)</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>机构偏多</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
@@ -1379,74 +1376,74 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>390.05</v>
+        <v>264.98</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>384.18 - 389.57</t>
+          <t>262.26 - 265.92</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>386.88</v>
+        <v>264.09</v>
       </c>
       <c r="F11" t="n">
-        <v>355.93</v>
+        <v>250.38</v>
       </c>
       <c r="G11" t="n">
-        <v>410.8</v>
+        <v>274.15</v>
       </c>
       <c r="H11" t="n">
-        <v>79.64</v>
+        <v>66.59</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0.23</v>
+        <v>0.05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.34</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.39</v>
+        <v>-0.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="O11" t="n">
-        <v>1.65</v>
+        <v>0.42</v>
       </c>
       <c r="P11" t="n">
-        <v>17527906304</v>
+        <v>156803694592</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>趋势未启动，仅观察</t>
+          <t>主升浪建仓/加仓</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>58.52</v>
+        <v>68.42</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>明确吸筹</t>
+          <t>强趋势回撤</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>uptrend</t>
+          <t>strong_uptrend</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1456,7 +1453,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>机构偏多</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
@@ -1468,84 +1465,84 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SKYT</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.83</v>
+        <v>51.34</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30.24 - 30.66</t>
+          <t>50.97 - 51.68</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>30.45</v>
+        <v>51.33</v>
       </c>
       <c r="F12" t="n">
-        <v>28.01</v>
+        <v>48.67</v>
       </c>
       <c r="G12" t="n">
-        <v>32.3</v>
+        <v>54.24</v>
       </c>
       <c r="H12" t="n">
-        <v>96.61</v>
+        <v>79.53</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>94.25</v>
+        <v>-0.25</v>
       </c>
       <c r="K12" t="n">
-        <v>97.33</v>
+        <v>-0.29</v>
       </c>
       <c r="L12" t="n">
-        <v>0.61</v>
+        <v>0.05</v>
       </c>
       <c r="M12" t="n">
-        <v>0.97</v>
+        <v>0.14</v>
       </c>
       <c r="N12" t="n">
-        <v>0.52</v>
+        <v>0.87</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.53</v>
+        <v>0.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1400419840</v>
+        <v>77248823296</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>趋势未启动，仅观察</t>
+          <t>主升浪建仓/加仓</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>49.5</v>
+        <v>63.43</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>底部试探</t>
+          <t>极度缩量(隐蔽吸筹)</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>trend_pullback</t>
+          <t>strong_uptrend</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>防御性对冲</t>
         </is>
       </c>
     </row>
@@ -1557,52 +1554,52 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DOO</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>77.56</v>
+        <v>48.43</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>76.81 - 77.89</t>
+          <t>48.21 - 48.88</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>77.34999999999999</v>
+        <v>48.54</v>
       </c>
       <c r="F13" t="n">
-        <v>73.34</v>
+        <v>46.03</v>
       </c>
       <c r="G13" t="n">
-        <v>80.29000000000001</v>
+        <v>50.38</v>
       </c>
       <c r="H13" t="n">
-        <v>85.53</v>
+        <v>99.02</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>8.73</v>
+        <v>0.09</v>
       </c>
       <c r="K13" t="n">
-        <v>8.57</v>
+        <v>-0.32</v>
       </c>
       <c r="L13" t="n">
-        <v>0.14</v>
+        <v>0.68</v>
       </c>
       <c r="M13" t="n">
-        <v>0.44</v>
+        <v>0.08</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.28</v>
       </c>
       <c r="P13" t="n">
-        <v>5727157248</v>
+        <v>22566311936</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1611,15 +1608,15 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>趋势未启动，仅观察</t>
+          <t>仅跟踪</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>47.37</v>
+        <v>51.91</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>量价中性</t>
+          <t>强趋势回撤</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1629,69 +1626,69 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>extended(超买)</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>机构偏多</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>SKYT</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>184.89</v>
+        <v>29.46</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>185.02 - 187.57</t>
+          <t>29.20 - 29.61</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>186.29</v>
+        <v>29.41</v>
       </c>
       <c r="F14" t="n">
-        <v>176.72</v>
+        <v>27.41</v>
       </c>
       <c r="G14" t="n">
-        <v>209.66</v>
+        <v>32.24</v>
       </c>
       <c r="H14" t="n">
-        <v>68.45999999999999</v>
+        <v>95.83</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>0.65</v>
+        <v>94.25</v>
       </c>
       <c r="K14" t="n">
-        <v>0.67</v>
+        <v>97.33</v>
       </c>
       <c r="L14" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>0.97</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7</v>
+        <v>0.52</v>
       </c>
       <c r="O14" t="n">
-        <v>0.64</v>
+        <v>-1.53</v>
       </c>
       <c r="P14" t="n">
-        <v>4596713914368</v>
+        <v>1400419840</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1704,11 +1701,11 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>46.96</v>
+        <v>49.35</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>量价中性</t>
+          <t>底部试探</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1718,7 +1715,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>distribution</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -1730,61 +1727,61 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>REX</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>35.75</v>
+        <v>44.06</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>35.50 - 36.00</t>
+          <t>43.95 - 44.56</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>35.75</v>
+        <v>44.26</v>
       </c>
       <c r="F15" t="n">
-        <v>32.94</v>
+        <v>41.98</v>
       </c>
       <c r="G15" t="n">
-        <v>37.11</v>
+        <v>45.93</v>
       </c>
       <c r="H15" t="n">
-        <v>81.31</v>
+        <v>62.8</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.04</v>
+        <v>0.75</v>
       </c>
       <c r="K15" t="n">
-        <v>0.03</v>
+        <v>0.84</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M15" t="n">
-        <v>0.09</v>
+        <v>0.36</v>
       </c>
       <c r="N15" t="n">
-        <v>0.83</v>
+        <v>1.03</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.03</v>
+        <v>0.71</v>
       </c>
       <c r="P15" t="n">
-        <v>1161643136</v>
+        <v>11845195776</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1793,16 +1790,16 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>44.31</v>
+        <v>44.9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>明确吸筹</t>
+          <t>量价中性</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>strong_uptrend</t>
+          <t>uptrend</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1819,61 +1816,61 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>REX</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>44.28</v>
+        <v>35.56</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.18 - 44.79</t>
+          <t>35.31 - 35.81</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>44.49</v>
+        <v>35.56</v>
       </c>
       <c r="F16" t="n">
-        <v>42.2</v>
+        <v>32.94</v>
       </c>
       <c r="G16" t="n">
-        <v>46.17</v>
+        <v>36.91</v>
       </c>
       <c r="H16" t="n">
-        <v>62.41</v>
+        <v>81.78</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.75</v>
+        <v>-0.04</v>
       </c>
       <c r="K16" t="n">
-        <v>0.84</v>
+        <v>0.03</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.36</v>
+        <v>0.09</v>
       </c>
       <c r="N16" t="n">
-        <v>1.03</v>
+        <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>0.71</v>
+        <v>-0.03</v>
       </c>
       <c r="P16" t="n">
-        <v>11845195776</v>
+        <v>1161643136</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1882,16 +1879,16 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>42.69</v>
+        <v>44.41</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>量价中性</t>
+          <t>明确吸筹</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>uptrend</t>
+          <t>strong_uptrend</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1913,56 +1910,56 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1524.31</v>
+        <v>372.14</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1496.42 - 1517.46</t>
+          <t>368.19 - 373.33</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1506.94</v>
+        <v>370.76</v>
       </c>
       <c r="F17" t="n">
-        <v>1428.06</v>
+        <v>351.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1582.16</v>
+        <v>389.12</v>
       </c>
       <c r="H17" t="n">
-        <v>89.51000000000001</v>
+        <v>76.28</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.39</v>
+        <v>0.14</v>
       </c>
       <c r="K17" t="n">
-        <v>0.41</v>
+        <v>0.15</v>
       </c>
       <c r="L17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="O17" t="n">
-        <v>0.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>203221909504</v>
+        <v>70620479488</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1971,26 +1968,26 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>32.82</v>
+        <v>43.13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>量价中性</t>
+          <t>极度缩量(隐蔽吸筹)</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>trend_pullback</t>
+          <t>strong_uptrend</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>防御性对冲</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
@@ -2002,52 +1999,52 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>AVO</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>154</v>
+        <v>14.19</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>154.10 - 156.23</t>
+          <t>14.11 - 14.30</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>155.17</v>
+        <v>14.2</v>
       </c>
       <c r="F18" t="n">
-        <v>147.2</v>
+        <v>13.47</v>
       </c>
       <c r="G18" t="n">
-        <v>161.01</v>
+        <v>14.74</v>
       </c>
       <c r="H18" t="n">
-        <v>87.91</v>
+        <v>66.03</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.44</v>
+        <v>-0.08</v>
       </c>
       <c r="K18" t="n">
-        <v>0.44</v>
+        <v>-0.04</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="M18" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0.34</v>
       </c>
       <c r="O18" t="n">
-        <v>0.54</v>
+        <v>0.39</v>
       </c>
       <c r="P18" t="n">
-        <v>34499227648</v>
+        <v>1023273280</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2056,15 +2053,15 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>量价支持不足</t>
+          <t>趋势未启动，仅观察</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>51.96</v>
+        <v>39.89</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>量价中性</t>
+          <t>极度缩量(隐蔽吸筹)</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2091,52 +2088,52 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>415.56</v>
+        <v>177.19</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>412.69 - 418.43</t>
+          <t>178.22 - 180.66</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>415.56</v>
+        <v>179.44</v>
       </c>
       <c r="F19" t="n">
-        <v>394.05</v>
+        <v>170.27</v>
       </c>
       <c r="G19" t="n">
-        <v>431.33</v>
+        <v>209.37</v>
       </c>
       <c r="H19" t="n">
-        <v>97.87</v>
+        <v>63.34</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8</v>
+        <v>0.65</v>
       </c>
       <c r="K19" t="n">
-        <v>1.75</v>
+        <v>0.67</v>
       </c>
       <c r="L19" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="M19" t="n">
-        <v>0.23</v>
+        <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02</v>
+        <v>0.64</v>
       </c>
       <c r="P19" t="n">
-        <v>469596241920</v>
+        <v>4596713914368</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2145,25 +2142,25 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>量价支持不足</t>
+          <t>趋势未启动，仅观察</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>50.96</v>
+        <v>34.29</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>量价中性</t>
+          <t>高位放量分歧</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>strong_uptrend</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>distribution</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2180,84 +2177,84 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GLDD</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.91</v>
+        <v>1524.55</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>16.80 - 17.03</t>
+          <t>1504.34 - 1525.37</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>16.91</v>
+        <v>1514.85</v>
       </c>
       <c r="F20" t="n">
-        <v>16.03</v>
+        <v>1435.95</v>
       </c>
       <c r="G20" t="n">
-        <v>17.55</v>
+        <v>1572.71</v>
       </c>
       <c r="H20" t="n">
-        <v>88.04000000000001</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="I20" t="n">
         <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.36</v>
+        <v>0.39</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.38</v>
+        <v>0.41</v>
       </c>
       <c r="L20" t="n">
-        <v>0.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.15</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>0.28</v>
+        <v>0.68</v>
       </c>
       <c r="P20" t="n">
-        <v>1150776576</v>
+        <v>203221909504</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>量价支持不足</t>
+          <t>趋势未启动，仅观察</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>48.39</v>
+        <v>30.9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>量价中性</t>
+          <t>底部试探</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>strong_uptrend</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>防御性对冲</t>
         </is>
       </c>
     </row>
@@ -2269,56 +2266,56 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>641.63</v>
+        <v>156.24</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>638.09 - 646.94</t>
+          <t>154.88 - 157.03</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>642.51</v>
+        <v>155.95</v>
       </c>
       <c r="F21" t="n">
-        <v>609.3099999999999</v>
+        <v>147.86</v>
       </c>
       <c r="G21" t="n">
-        <v>674.15</v>
+        <v>161.88</v>
       </c>
       <c r="H21" t="n">
-        <v>81.73</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="I21" t="n">
         <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>1.55</v>
+        <v>0.44</v>
       </c>
       <c r="K21" t="n">
-        <v>1.61</v>
+        <v>0.44</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="M21" t="n">
-        <v>0.77</v>
+        <v>0.16</v>
       </c>
       <c r="N21" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="P21" t="n">
-        <v>148541177856</v>
+        <v>34499227648</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2327,7 +2324,7 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>46.08</v>
+        <v>52.25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2346,7 +2343,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>机构偏多</t>
         </is>
       </c>
     </row>
@@ -2358,56 +2355,56 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OLPX</t>
+          <t>RCI</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.67</v>
+        <v>39.93</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.66 - 1.68</t>
+          <t>39.61 - 40.16</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.67</v>
+        <v>39.88</v>
       </c>
       <c r="F22" t="n">
-        <v>1.58</v>
+        <v>37.81</v>
       </c>
       <c r="G22" t="n">
-        <v>1.73</v>
+        <v>41.4</v>
       </c>
       <c r="H22" t="n">
-        <v>70.59</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.25</v>
+        <v>0.33</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.17</v>
+        <v>0.37</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.04</v>
+        <v>0.13</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.01</v>
+        <v>0.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.98</v>
+        <v>0.65</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7</v>
+        <v>1.04</v>
       </c>
       <c r="P22" t="n">
-        <v>1101394688</v>
+        <v>21593073664</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2416,7 +2413,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>31.22</v>
+        <v>52.1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2435,88 +2432,91 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>防御性对冲</t>
+          <t>机构偏多</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DBRG</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.41</v>
+        <v>412.37</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15.28 - 15.49</t>
+          <t>408.44 - 414.13</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>15.38</v>
+        <v>411.29</v>
       </c>
       <c r="F23" t="n">
-        <v>14.58</v>
+        <v>389.95</v>
       </c>
       <c r="G23" t="n">
-        <v>15.96</v>
+        <v>431.21</v>
       </c>
       <c r="H23" t="n">
-        <v>80.44</v>
+        <v>97.69</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.75</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.95</v>
+        <v>0.57</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.02</v>
+        <v>0.23</v>
       </c>
       <c r="N23" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.39</v>
+        <v>0.02</v>
       </c>
       <c r="P23" t="n">
-        <v>2995012352</v>
+        <v>469596241920</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>阶段不明，仅观察</t>
+          <t>量价支持不足</t>
         </is>
       </c>
       <c r="S23" t="n">
-        <v>50.89</v>
+        <v>50.93</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>极度缩量(隐蔽吸筹)</t>
+          <t>量价中性</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>uptrend</t>
+          <t>strong_uptrend</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -2533,52 +2533,52 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>GLDD</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>876.46</v>
+        <v>16.95</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>850.33 - 862.43</t>
+          <t>16.80 - 17.04</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>856.38</v>
+        <v>16.92</v>
       </c>
       <c r="F24" t="n">
-        <v>808.6799999999999</v>
+        <v>16.04</v>
       </c>
       <c r="G24" t="n">
-        <v>911.91</v>
+        <v>17.56</v>
       </c>
       <c r="H24" t="n">
-        <v>92.56</v>
+        <v>87.8</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>6.57</v>
+        <v>-0.36</v>
       </c>
       <c r="K24" t="n">
-        <v>6.72</v>
+        <v>-0.38</v>
       </c>
       <c r="L24" t="n">
-        <v>0.04</v>
+        <v>0.26</v>
       </c>
       <c r="M24" t="n">
-        <v>0.43</v>
+        <v>0.15</v>
       </c>
       <c r="N24" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="O24" t="n">
-        <v>1.06</v>
+        <v>0.28</v>
       </c>
       <c r="P24" t="n">
-        <v>237679427584</v>
+        <v>1150776576</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2587,15 +2587,15 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>阶段不明，小仓试探</t>
+          <t>量价支持不足</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>75</v>
+        <v>48.35</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>明确吸筹</t>
+          <t>量价中性</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>防御性对冲</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
@@ -2622,52 +2622,52 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CDRE</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>43.69</v>
+        <v>64.84</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>42.94 - 43.54</t>
+          <t>64.43 - 65.33</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>43.24</v>
+        <v>64.88</v>
       </c>
       <c r="F25" t="n">
-        <v>40.98</v>
+        <v>61.52</v>
       </c>
       <c r="G25" t="n">
-        <v>45.35</v>
+        <v>67.34</v>
       </c>
       <c r="H25" t="n">
-        <v>74.79000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
-        <v>1.99</v>
+        <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>1.99</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>0.42</v>
+        <v>0.15</v>
       </c>
       <c r="M25" t="n">
         <v>0.14</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="O25" t="n">
-        <v>0.52</v>
+        <v>0.09</v>
       </c>
       <c r="P25" t="n">
-        <v>1729377664</v>
+        <v>7265496064</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2676,100 +2676,100 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>非趋势结构，仅观察</t>
+          <t>量价支持不足</t>
         </is>
       </c>
       <c r="S25" t="n">
-        <v>37.63</v>
+        <v>38.39</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>趋势中资金分歧</t>
+          <t>量价中性</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>range</t>
+          <t>uptrend</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>防御性对冲</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>OLPX</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>321.7</v>
+        <v>1.61</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>312.05 - 315.73</t>
+          <t>1.60 - 1.62</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>313.51</v>
+        <v>1.61</v>
       </c>
       <c r="F26" t="n">
-        <v>296.86</v>
+        <v>1.53</v>
       </c>
       <c r="G26" t="n">
-        <v>333.91</v>
+        <v>1.67</v>
       </c>
       <c r="H26" t="n">
-        <v>72.11</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>1.73</v>
+        <v>-0.25</v>
       </c>
       <c r="K26" t="n">
-        <v>1.88</v>
+        <v>-0.17</v>
       </c>
       <c r="L26" t="n">
-        <v>0.16</v>
+        <v>-0.04</v>
       </c>
       <c r="M26" t="n">
-        <v>0.31</v>
+        <v>-0.01</v>
       </c>
       <c r="N26" t="n">
-        <v>0.79</v>
+        <v>0.98</v>
       </c>
       <c r="O26" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="P26" t="n">
-        <v>1501703700480</v>
+        <v>1101394688</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>非趋势结构，仅观察</t>
+          <t>量价支持不足</t>
         </is>
       </c>
       <c r="S26" t="n">
-        <v>37.37</v>
+        <v>30.78</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2778,101 +2778,101 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>downtrend</t>
+          <t>strong_uptrend</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>distribution</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>防御性对冲</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>CASY</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>135.94</v>
+        <v>685.59</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>133.94 - 135.82</t>
+          <t>680.15 - 689.61</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>134.88</v>
+        <v>684.88</v>
       </c>
       <c r="F27" t="n">
-        <v>125.74</v>
+        <v>649.4</v>
       </c>
       <c r="G27" t="n">
-        <v>142.61</v>
+        <v>725.5700000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>60.97</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>6.7</v>
+        <v>0.14</v>
       </c>
       <c r="K27" t="n">
-        <v>6.48</v>
+        <v>0.14</v>
       </c>
       <c r="L27" t="n">
-        <v>0.7</v>
+        <v>0.14</v>
       </c>
       <c r="M27" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="N27" t="n">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="O27" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="P27" t="n">
-        <v>326248235008</v>
+        <v>25047607296</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>非趋势结构，仅观察</t>
+          <t>量价支持不足</t>
         </is>
       </c>
       <c r="S27" t="n">
-        <v>35.53</v>
+        <v>29.95</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>量价中性</t>
+          <t>高位滞涨(出货嫌疑)</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>downtrend</t>
+          <t>strong_uptrend</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>distribution</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -2884,84 +2884,84 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>ELE</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>307.15</v>
+        <v>23.63</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>304.07 - 308.31</t>
+          <t>23.09 - 23.42</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>306.19</v>
+        <v>23.26</v>
       </c>
       <c r="F28" t="n">
-        <v>290.29</v>
+        <v>21.4</v>
       </c>
       <c r="G28" t="n">
-        <v>317.85</v>
+        <v>24.16</v>
       </c>
       <c r="H28" t="n">
-        <v>82.36</v>
+        <v>93.78</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3</v>
+        <v>1.18</v>
       </c>
       <c r="K28" t="n">
-        <v>0.31</v>
+        <v>0.73</v>
       </c>
       <c r="L28" t="n">
-        <v>0.18</v>
+        <v>0.84</v>
       </c>
       <c r="M28" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O28" t="n">
         <v>0.36</v>
       </c>
-      <c r="N28" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0.23</v>
-      </c>
       <c r="P28" t="n">
-        <v>3700593524736</v>
+        <v>1435464832</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>非趋势结构，仅观察</t>
+          <t>阶段不明，仅观察</t>
         </is>
       </c>
       <c r="S28" t="n">
-        <v>35</v>
+        <v>59.46</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>量价中性</t>
+          <t>底部试探</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>downtrend</t>
+          <t>strong_uptrend</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>distribution</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -2978,65 +2978,65 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>41.91</v>
+        <v>118.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>41.62 - 42.20</t>
+          <t>116.94 - 118.57</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>41.91</v>
+        <v>117.75</v>
       </c>
       <c r="F29" t="n">
-        <v>39.74</v>
+        <v>111.62</v>
       </c>
       <c r="G29" t="n">
-        <v>43.5</v>
+        <v>122.24</v>
       </c>
       <c r="H29" t="n">
-        <v>68.98</v>
+        <v>92.06</v>
       </c>
       <c r="I29" t="n">
         <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>1.78</v>
+        <v>0.47</v>
       </c>
       <c r="K29" t="n">
-        <v>1.75</v>
+        <v>0.45</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4</v>
+        <v>0.09</v>
       </c>
       <c r="N29" t="n">
-        <v>0.96</v>
+        <v>0.68</v>
       </c>
       <c r="O29" t="n">
-        <v>0.59</v>
+        <v>0.34</v>
       </c>
       <c r="P29" t="n">
-        <v>6172133888</v>
+        <v>52180451328</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>非趋势结构，仅观察</t>
+          <t>阶段不明，仅观察</t>
         </is>
       </c>
       <c r="S29" t="n">
-        <v>29.38</v>
+        <v>43.57</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>range</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3055,272 +3055,984 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>防御性对冲</t>
+          <t>中性</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>84.59</v>
+        <v>41.88</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>84.08 - 85.24</t>
+          <t>41.58 - 42.16</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>84.66</v>
+        <v>41.87</v>
       </c>
       <c r="F30" t="n">
-        <v>77.89</v>
+        <v>39.7</v>
       </c>
       <c r="G30" t="n">
-        <v>99.28</v>
+        <v>43.46</v>
       </c>
       <c r="H30" t="n">
-        <v>28.08</v>
+        <v>70.91</v>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
-        <v>0.29</v>
+        <v>1.78</v>
       </c>
       <c r="K30" t="n">
-        <v>0.33</v>
+        <v>1.75</v>
       </c>
       <c r="L30" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="O30" t="n">
-        <v>2.45</v>
+        <v>0.59</v>
       </c>
       <c r="P30" t="n">
-        <v>350804246528</v>
+        <v>6172133888</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>非趋势结构，仅观察</t>
+          <t>阶段不明，仅观察</t>
         </is>
       </c>
       <c r="S30" t="n">
-        <v>24.29</v>
+        <v>41.59</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>趋势中资金分歧</t>
+          <t>极度缩量(隐蔽吸筹)</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>downtrend</t>
+          <t>uptrend</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>distribution</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>机构偏多</t>
+          <t>防御性对冲</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>FOR</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>203.68</v>
+        <v>28.72</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>201.94 - 204.75</t>
+          <t>28.49 - 28.89</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>203.35</v>
+        <v>28.69</v>
       </c>
       <c r="F31" t="n">
-        <v>192.81</v>
+        <v>27.2</v>
       </c>
       <c r="G31" t="n">
-        <v>219.02</v>
+        <v>30.3</v>
       </c>
       <c r="H31" t="n">
-        <v>41.16</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>2.13</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>2.17</v>
+        <v>-0.06</v>
       </c>
       <c r="L31" t="n">
-        <v>0.34</v>
+        <v>0.09</v>
       </c>
       <c r="M31" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="O31" t="n">
-        <v>0.6</v>
+        <v>1.44</v>
       </c>
       <c r="P31" t="n">
-        <v>336932569088</v>
+        <v>1437192320</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>非趋势结构，仅观察</t>
+          <t>阶段不明，仅观察</t>
         </is>
       </c>
       <c r="S31" t="n">
-        <v>20.67</v>
+        <v>35.42</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>高位放量分歧</t>
+          <t>量价中性</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>downtrend</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>distribution</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>机构偏多</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TFPM</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>41.07 - 41.65</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="F32" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="G32" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="H32" t="n">
+        <v>90.77</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="P32" t="n">
+        <v>8273842176</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>阶段不明，小仓试探</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>75</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>明确吸筹</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>strong_uptrend</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>机构偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CRS</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>398.07</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>390.19 - 395.69</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>392.94</v>
+      </c>
+      <c r="F33" t="n">
+        <v>372.34</v>
+      </c>
+      <c r="G33" t="n">
+        <v>415.4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>88.98</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>20020940800</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>阶段不明，小仓试探</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>75</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>明确吸筹</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>strong_uptrend</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CDRE</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>43.71 - 44.32</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>44.01</v>
+      </c>
+      <c r="F34" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="G34" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="H34" t="n">
+        <v>76.13</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1729377664</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>非趋势结构，仅观察</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>37.87</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>趋势中资金分歧</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>319.55</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>315.27 - 319.68</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>317.47</v>
+      </c>
+      <c r="F35" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="G35" t="n">
+        <v>333.83</v>
+      </c>
+      <c r="H35" t="n">
+        <v>70.02</v>
+      </c>
+      <c r="I35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1501703700480</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>非趋势结构，仅观察</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>量价中性</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>downtrend</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>distribution</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>311.43</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>305.04 - 309.34</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>307.19</v>
+      </c>
+      <c r="F36" t="n">
+        <v>291.07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>319.01</v>
+      </c>
+      <c r="H36" t="n">
+        <v>83.95999999999999</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3700593524736</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>非趋势结构，仅观察</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>量价中性</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>downtrend</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>distribution</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>96.23999999999999</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>93.61 - 94.94</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>94.27</v>
+      </c>
+      <c r="F37" t="n">
+        <v>86.73</v>
+      </c>
+      <c r="G37" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="H37" t="n">
+        <v>38.16</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P37" t="n">
+        <v>350804246528</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>非趋势结构，仅观察</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>高位放量分歧</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>distribution</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>机构偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>137.19</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>134.95 - 136.85</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>135.9</v>
+      </c>
+      <c r="F38" t="n">
+        <v>125.74</v>
+      </c>
+      <c r="G38" t="n">
+        <v>142.66</v>
+      </c>
+      <c r="H38" t="n">
+        <v>64.22</v>
+      </c>
+      <c r="I38" t="n">
+        <v>5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K38" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P38" t="n">
+        <v>326248235008</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>非趋势结构，仅观察</t>
+        </is>
+      </c>
+      <c r="S38" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>趋势中资金分歧</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>downtrend</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>distribution</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>200.21</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>198.08 - 200.84</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>199.46</v>
+      </c>
+      <c r="F39" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>218.89</v>
+      </c>
+      <c r="H39" t="n">
+        <v>38.97</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P39" t="n">
+        <v>336932569088</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>非趋势结构，仅观察</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>高位放量分歧</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>downtrend</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>distribution</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>ORCL</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>150.31</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>147.57 - 149.64</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>148.61</v>
-      </c>
-      <c r="F32" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="G32" t="n">
-        <v>156.01</v>
-      </c>
-      <c r="H32" t="n">
-        <v>26.26</v>
-      </c>
-      <c r="I32" t="n">
+      <c r="C40" t="n">
+        <v>145.4</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>143.21 - 145.22</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>144.21</v>
+      </c>
+      <c r="F40" t="n">
+        <v>136.69</v>
+      </c>
+      <c r="G40" t="n">
+        <v>155.83</v>
+      </c>
+      <c r="H40" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="I40" t="n">
         <v>3</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J40" t="n">
         <v>0.95</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K40" t="n">
         <v>0.91</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L40" t="n">
         <v>0.14</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M40" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N40" t="n">
         <v>0.44</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O40" t="n">
         <v>-0.46</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P40" t="n">
         <v>433484759040</v>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>非趋势结构，仅观察</t>
         </is>
       </c>
-      <c r="S32" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="T32" t="inlineStr">
+      <c r="S40" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="T40" t="inlineStr">
         <is>
           <t>派发阶段</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>downtrend</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>distribution</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
